--- a/data/outputs/irr_scores.xlsx
+++ b/data/outputs/irr_scores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,34 +463,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>CHW Empowerment Through Training</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.834</v>
+        <v>0.711</v>
       </c>
       <c r="C2" t="n">
-        <v>0.357</v>
+        <v>0.449</v>
       </c>
       <c r="D2" t="n">
-        <v>0.333</v>
+        <v>0.483</v>
       </c>
       <c r="E2" t="n">
-        <v>0.712</v>
+        <v>0.623</v>
       </c>
       <c r="F2" t="n">
-        <v>0.667</v>
+        <v>0.76</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>Menstrual Hygiene Education and Challenges</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.958</v>
+        <v>0.995</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.923</v>
+        <v>0.993</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -509,94 +509,823 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>community impact</t>
+          <t>Drug Abuse: Environment and Awareness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
+        <v>-0.004</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0.931</v>
+        <v>-0.008</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models o3 vs claude</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>CHW-Led Infectious Disease Management</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.636</v>
+        <v>0.985</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.125</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.452</v>
+        <v>0.975</v>
       </c>
       <c r="F5" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>No variation in binary labels for models gpt vs claude</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>knowledge sharing</t>
+          <t>Water Quality, Sanitation, and Hygiene</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0.843</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.627</v>
       </c>
       <c r="E6" t="n">
-        <v>0.158</v>
+        <v>0.794</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>No variation in binary labels for models claude vs gemini</t>
-        </is>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>Personal Disease Management and Adherence</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Nutrition Education and Food Access</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Sexual and Reproductive Health Education</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Gender-Based Violence (GBV) and Child Protection</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Mental Health Awareness and Support</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Community Empowerment Through Education</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Resource and Material Distribution</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Trust and Cultural Mediation</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Successful Outcomes</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Material or Training Requests</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.124</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models o3 vs claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Elderly Served</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N/A (no variability)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models o3 vs claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Financial Hardship</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Social Isolation</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models o3 vs claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Mental or Emotional Distress</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Overburdened CHWs</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models o3 vs claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Lack of Follow-Through</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models o3 vs claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
           <t>OVERALL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/irr_scores.xlsx
+++ b/data/outputs/irr_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,108 +454,206 @@
           <t>percent_agreement</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cohen_notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CHW Empowered Through Training</t>
+          <t>Group Based Health Education</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="C2" t="n">
-        <v>0.702</v>
+        <v>0.745</v>
       </c>
       <c r="D2" t="n">
-        <v>0.702</v>
+        <v>0.746</v>
       </c>
       <c r="E2" t="n">
-        <v>0.799</v>
+        <v>0.774</v>
       </c>
       <c r="F2" t="n">
-        <v>0.92</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Referrals and Advocacy</t>
+          <t>Individualized Support and Health Education</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.882</v>
+        <v>0.897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.351</v>
+        <v>0.758</v>
       </c>
       <c r="D3" t="n">
-        <v>0.387</v>
+        <v>0.759</v>
       </c>
       <c r="E3" t="n">
-        <v>0.83</v>
+        <v>0.865</v>
       </c>
       <c r="F3" t="n">
-        <v>0.68</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Community Empowerment Through Education</t>
+          <t>Cholera Education and Prevention</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.194</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.634</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models anthropic vs openai</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handing out Medical Supplies </t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.831</v>
-      </c>
+          <t>Direct Intervention for Cholera Cases</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>No variation in binary labels for models anthropic vs openai</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>Diabetes Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>HIV/AIDS Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Infectious Disease Prevention</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Tuberculosis Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>OVERALL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.878</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/irr_scores.xlsx
+++ b/data/outputs/irr_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,206 +454,900 @@
           <t>percent_agreement</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cohen_notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Group Based Health Education</t>
+          <t>CHW Empowered Through Training</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.824</v>
+        <v>0.927</v>
       </c>
       <c r="C2" t="n">
-        <v>0.745</v>
+        <v>0.841</v>
       </c>
       <c r="D2" t="n">
-        <v>0.746</v>
+        <v>0.841</v>
       </c>
       <c r="E2" t="n">
-        <v>0.774</v>
+        <v>0.904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>0.965</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Individualized Support and Health Education</t>
+          <t>Menstrual Hygiene Education and Challenges</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.897</v>
+        <v>0.989</v>
       </c>
       <c r="C3" t="n">
-        <v>0.758</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.759</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.865</v>
+        <v>0.986</v>
       </c>
       <c r="F3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>0.993</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cholera Education and Prevention</t>
+          <t>Drug Abuse: Environment and Awareness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+        <v>0.973</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.951</v>
+      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.964</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>No variation in binary labels for models anthropic vs openai</t>
-        </is>
+        <v>0.997</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Direct Intervention for Cholera Cases</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>CHW-Led Infectious Disease Management</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.956</v>
+      </c>
       <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>No variation in binary labels for models anthropic vs openai</t>
-        </is>
+        <v>0.944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Diabetes Education and Prevention</t>
+          <t>Water Quality, Sanitation, and Hygiene</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.995</v>
+        <v>0.974</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="E6" t="n">
-        <v>0.993</v>
+        <v>0.965</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>0.965</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>HIV/AIDS Education and Prevention</t>
+          <t>Personal Disease Management and Adherence</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.997</v>
+        <v>0.869</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.663</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.666</v>
       </c>
       <c r="E7" t="n">
-        <v>0.995</v>
+        <v>0.821</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>0.833</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Infectious Disease Prevention</t>
+          <t>Nutrition Education and Food Access</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.847</v>
+        <v>0.961</v>
       </c>
       <c r="C8" t="n">
-        <v>0.754</v>
+        <v>0.806</v>
       </c>
       <c r="D8" t="n">
-        <v>0.754</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801</v>
+        <v>0.948</v>
       </c>
       <c r="F8" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>0.969</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Tuberculosis Education and Prevention</t>
+          <t>Sexual and Reproductive Health Education</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C9" t="n">
-        <v>0.645</v>
+        <v>0.895</v>
       </c>
       <c r="D9" t="n">
-        <v>0.648</v>
+        <v>0.895</v>
       </c>
       <c r="E9" t="n">
-        <v>0.917</v>
+        <v>0.972</v>
       </c>
       <c r="F9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>0.962</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>Gender-Based Violence (GBV) and Child Protection</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Health Literacy and Misconceptions</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.861</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Mental Health Awareness and Support</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.944</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Referrals and Advocacy</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Handing out Medical Supplies </t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Monitoring and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.924</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Bridge Between Community and Health System</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.889</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Clinical Interventions by CHWs</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Mother and Infant Care</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Direct Clinical Outcomes</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Children Served</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.951</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Elderly Served</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Women Served</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Men Served</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.951</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Families Served</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.927</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Marginalized Groups Served</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.823</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Lack of Financial Resources for Healthcare</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Social Isolation or Emotional Distress</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Disease Burden</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Stigma or Discrimination</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Lack of Resources</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Systemic Barriers</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Overburdened CHWs</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Lack of Knowledge</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.979</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Group Based Health Education</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.896</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Individualized Support and Health Education</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.899</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Cholera Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Direct Intervention for Cholera Cases</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Diabetes Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>HIV/AIDS Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Infectious Disease Prevention</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.892</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Tuberculosis Education and Prevention</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>OVERALL</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
